--- a/ig/main/CodeSystem-terminologie-sms.xlsx
+++ b/ig/main/CodeSystem-terminologie-sms.xlsx
@@ -40,7 +40,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2026-09</t>
+    <t>2026-10</t>
   </si>
   <si>
     <t>Name</t>
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-04T10:00:00+00:00</t>
+    <t>2026-10-05T00:00:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -130,7 +130,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>72708</t>
+    <t>72971</t>
   </si>
   <si>
     <t>Code</t>

--- a/ig/main/CodeSystem-terminologie-sms.xlsx
+++ b/ig/main/CodeSystem-terminologie-sms.xlsx
@@ -31,10 +31,10 @@
     <t>Identifier</t>
   </si>
   <si>
-    <t>OID:2.16.840.1.113883.3.6905.2 (use: usual, )</t>
-  </si>
-  <si>
-    <t>https://smt.esante.gouv.fr/#terminologie-sms (use: secondary, )</t>
+    <t>OID:2.16.840.1.113883.3.6905.2 (use: usual)</t>
+  </si>
+  <si>
+    <t>https://smt.esante.gouv.fr/#terminologie-sms (use: secondary)</t>
   </si>
   <si>
     <t>Version</t>
